--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484094_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484094_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7041</v>
+        <v>4.3451</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1713</v>
+        <v>5.8684</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4672</v>
+        <v>-1.5233</v>
       </c>
       <c r="G2" t="n">
         <v>2.269</v>
@@ -610,13 +610,13 @@
         <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0293</v>
+        <v>-0.3883</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3716</v>
+        <v>-0.6744</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3423</v>
+        <v>0.2862</v>
       </c>
       <c r="V2" t="n">
         <v>1.4724</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8651</v>
+        <v>1.911</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1827</v>
+        <v>1.2847</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6824</v>
+        <v>0.6263</v>
       </c>
       <c r="G3" t="n">
         <v>1.7892</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0759</v>
+        <v>0.1219</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0623</v>
+        <v>0.0397</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1383</v>
+        <v>0.0822</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9483</v>
+        <v>-0.4677</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8264</v>
+        <v>-0.458</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1219</v>
+        <v>-0.0097</v>
       </c>
       <c r="G4" t="n">
         <v>0.1558</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1122</v>
+        <v>0.3684</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.4535</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1973</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. CRUZ JOBACHO</t>
+          <t>P. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.0657</v>
+        <v>-0.9330000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0392</v>
+        <v>0.2174</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0265</v>
+        <v>-1.1503</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5791</v>
+        <v>-1.0741</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0737</v>
+        <v>-0.2774</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5055</v>
+        <v>-0.7967</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.6643</v>
+        <v>0.121</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0509</v>
+        <v>0.121</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7153</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.9148</v>
+        <v>-1.1951</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1246</v>
+        <v>-0.3983</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7902</v>
+        <v>-0.7967</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1167</v>
+        <v>-0.3188</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1926</v>
+        <v>0.0964</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3093</v>
+        <v>-0.4152</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6032</v>
+        <v>-0.532</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8097</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2065</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MORENO MARTIN</t>
+          <t>A. CRUZ JOBACHO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3754</v>
+        <v>-1.548</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2531</v>
+        <v>-0.0165</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1223</v>
+        <v>-1.5315</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0741</v>
+        <v>-2.5791</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2774</v>
+        <v>-1.0737</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7967</v>
+        <v>-1.5055</v>
       </c>
       <c r="J6" t="n">
-        <v>0.121</v>
+        <v>-0.6643</v>
       </c>
       <c r="K6" t="n">
-        <v>0.121</v>
+        <v>0.0509</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.7153</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1951</v>
+        <v>-1.9148</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3983</v>
+        <v>-1.1246</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7967</v>
+        <v>-0.7902</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9919</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7612</v>
+        <v>-0.3656</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3872</v>
+        <v>-0.1957</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.532</v>
+        <v>0.6032</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.8097</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.532</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.8588</v>
+        <v>-3.3244</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1182</v>
+        <v>-0.4316</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.977</v>
+        <v>-2.8928</v>
       </c>
       <c r="G7" t="n">
         <v>0.6025</v>
@@ -1000,13 +1000,13 @@
         <v>0.5952</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8723</v>
+        <v>0.4067</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0487</v>
+        <v>0.4988</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1763</v>
+        <v>-0.0922</v>
       </c>
       <c r="V7" t="n">
         <v>-2.9449</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.0427</v>
+        <v>-3.3609</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4748</v>
+        <v>-0.1858</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5679</v>
+        <v>-3.1751</v>
       </c>
       <c r="G8" t="n">
         <v>-3.2556</v>
@@ -1078,13 +1078,13 @@
         <v>1.7855</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5292</v>
+        <v>-0.8474</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5667</v>
+        <v>-0.2776</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9625</v>
+        <v>-0.5697</v>
       </c>
       <c r="V8" t="n">
         <v>0.9405</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.2825</v>
+        <v>-4.4537</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6927</v>
+        <v>-1.9761</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5898</v>
+        <v>-2.4776</v>
       </c>
       <c r="G9" t="n">
         <v>-4.0011</v>
@@ -1156,13 +1156,13 @@
         <v>1.1903</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7267</v>
+        <v>0.5555</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4479</v>
+        <v>0.1645</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2788</v>
+        <v>0.391</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2065</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6567</v>
+        <v>-5.2003</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1267</v>
+        <v>-1.6142</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.53</v>
+        <v>-3.5861</v>
       </c>
       <c r="G10" t="n">
         <v>-4.0335</v>
@@ -1234,13 +1234,13 @@
         <v>0.9919</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2379</v>
+        <v>0.6943</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.2722</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4783</v>
+        <v>0.4222</v>
       </c>
       <c r="V10" t="n">
         <v>-0.8692</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. NOGUES MARTIN</t>
+          <t>M. GARCIA IBAÑEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.89</v>
+        <v>-5.6962</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0193</v>
+        <v>-5.5255</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.8707</v>
+        <v>-0.1707</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2616</v>
+        <v>-2.8139</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.9619</v>
+        <v>-1.184</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7003</v>
+        <v>-1.6299</v>
       </c>
       <c r="J11" t="n">
-        <v>3.4563</v>
+        <v>-2.0498</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2868</v>
+        <v>0.5454</v>
       </c>
       <c r="L11" t="n">
-        <v>5.7431</v>
+        <v>-2.5952</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.7179</v>
+        <v>-0.7642</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.6751</v>
+        <v>-1.7294</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0428</v>
+        <v>0.9653</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.9758</v>
+        <v>-3.3725</v>
       </c>
       <c r="Q11" t="n">
         <v>-4.9596</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9838</v>
+        <v>1.5871</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4943</v>
+        <v>-0.1842</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0115</v>
+        <v>0.0114</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4828</v>
+        <v>-0.1957</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.1469</v>
+        <v>0.6745</v>
       </c>
       <c r="W11" t="n">
         <v>1.4724</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.6194</v>
+        <v>-0.7979000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. GARCIA IBAÑEZ</t>
+          <t>E. NOGUES MARTIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5391</v>
+        <v>-6.1151</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.2001</v>
+        <v>-0.0761</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.339</v>
+        <v>-6.039</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.8139</v>
+        <v>-1.2616</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.184</v>
+        <v>-5.9619</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6299</v>
+        <v>4.7003</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.0498</v>
+        <v>3.4563</v>
       </c>
       <c r="K12" t="n">
-        <v>0.5454</v>
+        <v>-2.2868</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5952</v>
+        <v>5.7431</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7642</v>
+        <v>-4.7179</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7294</v>
+        <v>-3.6751</v>
       </c>
       <c r="O12" t="n">
-        <v>0.9653</v>
+        <v>-1.0428</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.3725</v>
+        <v>-2.9758</v>
       </c>
       <c r="Q12" t="n">
         <v>-4.9596</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5871</v>
+        <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0271</v>
+        <v>0.2692</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6631</v>
+        <v>-0.0452</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.364</v>
+        <v>0.3145</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6745</v>
+        <v>-2.1469</v>
       </c>
       <c r="W12" t="n">
         <v>1.4724</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.09</v>
+        <v>-24.8432</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1601</v>
+        <v>-2.9133</v>
       </c>
       <c r="F13" t="n">
-        <v>-21.9299</v>
+        <v>-21.9298</v>
       </c>
       <c r="G13" t="n">
         <v>-14.2024</v>
@@ -1468,13 +1468,13 @@
         <v>12.895</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9351999999999998</v>
+        <v>0.3117000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8776999999999997</v>
+        <v>0.3693</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.05749999999999983</v>
+        <v>-0.05740000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-4.008900000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.1424</v>
+        <v>12.0474</v>
       </c>
       <c r="E14" t="n">
-        <v>11.5221</v>
+        <v>10.6039</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6203</v>
+        <v>1.4435</v>
       </c>
       <c r="G14" t="n">
         <v>4.0648</v>
@@ -1546,13 +1546,13 @@
         <v>2.9758</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5258</v>
+        <v>0.4308</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9184</v>
+        <v>0.0001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6075</v>
+        <v>0.4307</v>
       </c>
       <c r="V14" t="n">
         <v>5.7663</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0148</v>
+        <v>5.6856</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4601</v>
+        <v>4.7662</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5547</v>
+        <v>0.9195</v>
       </c>
       <c r="G15" t="n">
         <v>1.1364</v>
@@ -1624,13 +1624,13 @@
         <v>2.7774</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4427</v>
+        <v>0.2282</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3797</v>
+        <v>-0.0736</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.063</v>
+        <v>0.3017</v>
       </c>
       <c r="V15" t="n">
         <v>1.5437</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9453</v>
+        <v>5.3194</v>
       </c>
       <c r="E16" t="n">
-        <v>4.0249</v>
+        <v>4.1269</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9204</v>
+        <v>1.1925</v>
       </c>
       <c r="G16" t="n">
         <v>4.6498</v>
@@ -1702,13 +1702,13 @@
         <v>1.9838</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2834</v>
+        <v>0.0907</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5667</v>
+        <v>-0.4647</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2833</v>
+        <v>0.5554</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2065</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5133</v>
+        <v>4.2981</v>
       </c>
       <c r="E17" t="n">
-        <v>2.671</v>
+        <v>2.875</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8424</v>
+        <v>1.4231</v>
       </c>
       <c r="G17" t="n">
         <v>4.34</v>
@@ -1780,13 +1780,13 @@
         <v>2.579</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7635</v>
+        <v>0.0213</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3173</v>
+        <v>-0.1133</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4462</v>
+        <v>0.1345</v>
       </c>
       <c r="V17" t="n">
         <v>0.532</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4737</v>
+        <v>2.2692</v>
       </c>
       <c r="E18" t="n">
-        <v>3.678</v>
+        <v>3.83</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2043</v>
+        <v>-1.5608</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8214</v>
+        <v>3.8767</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0104</v>
+        <v>1.8646</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8318</v>
+        <v>2.012</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4771</v>
+        <v>3.5081</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7944</v>
+        <v>2.1828</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6827</v>
+        <v>1.3253</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6557</v>
+        <v>0.3686</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8048</v>
+        <v>-0.3181</v>
       </c>
       <c r="O18" t="n">
-        <v>0.149</v>
+        <v>0.6867</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9919</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9838</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6604</v>
+        <v>0.6107</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9863</v>
+        <v>0.5159</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3259</v>
+        <v>0.0949</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-2.2182</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>0.7979000000000001</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2065</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3687</v>
+        <v>2.2058</v>
       </c>
       <c r="E19" t="n">
-        <v>4.2381</v>
+        <v>3.2699</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8694</v>
+        <v>-1.064</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8767</v>
+        <v>0.8214</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8646</v>
+        <v>-0.0104</v>
       </c>
       <c r="I19" t="n">
-        <v>2.012</v>
+        <v>0.8318</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5081</v>
+        <v>2.4771</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1828</v>
+        <v>1.7944</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3253</v>
+        <v>0.6827</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3686</v>
+        <v>-1.6557</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3181</v>
+        <v>-1.8048</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6867</v>
+        <v>0.149</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.9919</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.3925</v>
       </c>
       <c r="T19" t="n">
-        <v>0.924</v>
+        <v>0.5782</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2137</v>
+        <v>-0.1857</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2182</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7979000000000001</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.0162</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0788</v>
+        <v>1.157</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8732</v>
+        <v>0.5671</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2056</v>
+        <v>0.5899</v>
       </c>
       <c r="G20" t="n">
         <v>1.1226</v>
@@ -2014,13 +2014,13 @@
         <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1746</v>
+        <v>-0.0964</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3685</v>
+        <v>0.0624</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.543</v>
+        <v>-0.1587</v>
       </c>
       <c r="V20" t="n">
         <v>-0.266</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.3859</v>
+        <v>0.442</v>
       </c>
       <c r="E21" t="n">
         <v>0.0861</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2998</v>
+        <v>0.3559</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1159</v>
@@ -2092,13 +2092,13 @@
         <v>0.1984</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0374</v>
+        <v>0.0935</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1247</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1621</v>
+        <v>0.2182</v>
       </c>
       <c r="V21" t="n">
         <v>0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4941</v>
+        <v>0.028</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8528</v>
+        <v>-1.5467</v>
       </c>
       <c r="F22" t="n">
-        <v>1.3587</v>
+        <v>1.5747</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4117</v>
@@ -2170,13 +2170,13 @@
         <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0646</v>
+        <v>0.5866</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0679</v>
+        <v>0.2381</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1325</v>
+        <v>0.3485</v>
       </c>
       <c r="V22" t="n">
         <v>0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4302</v>
+        <v>-1.2669</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8095</v>
+        <v>-3.1974</v>
       </c>
       <c r="F23" t="n">
-        <v>2.3794</v>
+        <v>1.9305</v>
       </c>
       <c r="G23" t="n">
         <v>-0.0648</v>
@@ -2248,13 +2248,13 @@
         <v>2.1822</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1541</v>
+        <v>0.3174</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6858</v>
+        <v>-0.0736</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8399</v>
+        <v>0.391</v>
       </c>
       <c r="V23" t="n">
         <v>0.266</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9088</v>
+        <v>-4.7353</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9614</v>
+        <v>-3.4512</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9474</v>
+        <v>-1.2841</v>
       </c>
       <c r="G24" t="n">
         <v>-3.2166</v>
@@ -2326,13 +2326,13 @@
         <v>1.7855</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5533</v>
+        <v>-0.3798</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.4874</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4443</v>
+        <v>0.1076</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9405</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>26.0898</v>
+        <v>27.4503</v>
       </c>
       <c r="E25" t="n">
         <v>21.9298</v>
       </c>
       <c r="F25" t="n">
-        <v>4.1602</v>
+        <v>5.5207</v>
       </c>
       <c r="G25" t="n">
         <v>14.2027</v>
@@ -2404,13 +2404,13 @@
         <v>19.8385</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9349999999999999</v>
+        <v>2.2955</v>
       </c>
       <c r="T25" t="n">
-        <v>0.05759999999999965</v>
+        <v>0.05740000000000006</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8777999999999998</v>
+        <v>2.2381</v>
       </c>
       <c r="V25" t="n">
         <v>4.008800000000001</v>
